--- a/docs/downloads/05/tbl_lighting_marovoay_madiromiongana.xlsx
+++ b/docs/downloads/05/tbl_lighting_marovoay_madiromiongana.xlsx
@@ -382,12 +382,6 @@
           <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -520,12 +514,6 @@
         <is>
           <t>Marovoay - Tous</t>
         </is>
-      </c>
-      <c r="C10">
-        <v>4</v>
-      </c>
-      <c r="D10">
-        <v>0.5</v>
       </c>
     </row>
     <row r="11">

--- a/docs/downloads/05/tbl_lighting_marovoay_madiromiongana.xlsx
+++ b/docs/downloads/05/tbl_lighting_marovoay_madiromiongana.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -398,7 +398,7 @@
         <v>6</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="4">
@@ -416,7 +416,7 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>5.9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -434,7 +434,7 @@
         <v>5</v>
       </c>
       <c r="D5">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="6">
@@ -445,14 +445,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Panneau Solaire En Marche ?</t>
+          <t>Piles</t>
         </is>
       </c>
       <c r="C6">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D6">
-        <v>12.3</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="7">
@@ -463,14 +463,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Piles</t>
+          <t>Pétrole Lampant</t>
         </is>
       </c>
       <c r="C7">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="D7">
-        <v>16.7</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="8">
@@ -481,32 +481,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pétrole Lampant</t>
+          <t>Solaire</t>
         </is>
       </c>
       <c r="C8">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="D8">
-        <v>47.8</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Solaire</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>22</v>
-      </c>
-      <c r="D9">
-        <v>10.8</v>
+          <t>Marovoay - Tous</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -515,6 +504,17 @@
           <t>Marovoay - Tous</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Autres</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>31</v>
+      </c>
+      <c r="D10">
+        <v>6</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -524,14 +524,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Batteries</t>
         </is>
       </c>
       <c r="C11">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="D11">
-        <v>3.6</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="12">
@@ -542,14 +542,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Batteries</t>
+          <t>Bois De Chauffe</t>
         </is>
       </c>
       <c r="C12">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="D12">
-        <v>7.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="13">
@@ -560,14 +560,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bois De Chauffe</t>
+          <t>Piles</t>
         </is>
       </c>
       <c r="C13">
-        <v>6</v>
+        <v>151</v>
       </c>
       <c r="D13">
-        <v>0.7</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="14">
@@ -578,14 +578,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Panneau Solaire En Marche ?</t>
+          <t>Pétrole Lampant</t>
         </is>
       </c>
       <c r="C14">
-        <v>163</v>
+        <v>283</v>
       </c>
       <c r="D14">
-        <v>18.8</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="15">
@@ -596,50 +596,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Piles</t>
+          <t>Solaire</t>
         </is>
       </c>
       <c r="C15">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="D15">
-        <v>17.5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Pétrole Lampant</t>
-        </is>
-      </c>
-      <c r="C16">
-        <v>283</v>
-      </c>
-      <c r="D16">
-        <v>32.7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Solaire</t>
-        </is>
-      </c>
-      <c r="C17">
-        <v>162</v>
-      </c>
-      <c r="D17">
-        <v>18.7</v>
+        <v>31.2</v>
       </c>
     </row>
   </sheetData>
